--- a/PCB/BOM_XAI_MB.xlsx
+++ b/PCB/BOM_XAI_MB.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_XAI Main Board_PCB1_2026-09" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_XAI Main Board_PCB1_2026-10" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>No.</t>
   </si>
@@ -109,58 +109,25 @@
     <t>4</t>
   </si>
   <si>
-    <t>PZ254V-11-03P</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>HDR-TH_3P-P2.54-V-M_PZ254V-11-03P</t>
-  </si>
-  <si>
-    <t>C2937625</t>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>RN1</t>
+  </si>
+  <si>
+    <t>RES-ARRAY-SMD_0404-4P-L1.0-W1.0-BL</t>
+  </si>
+  <si>
+    <t>YC122-JR-0710KL</t>
+  </si>
+  <si>
+    <t>YAGEO(国巨)</t>
+  </si>
+  <si>
+    <t>C695179</t>
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>SI1967DH-T1-GE3</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SOT-363_L2.0-W1.3-P0.65-LS2.1-BL</t>
-  </si>
-  <si>
-    <t>VISHAY(威世)</t>
-  </si>
-  <si>
-    <t>C435924</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>RN1</t>
-  </si>
-  <si>
-    <t>RES-ARRAY-SMD_0404-4P-L1.0-W1.0-BL</t>
-  </si>
-  <si>
-    <t>YC122-JR-0710KL</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>C695179</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>CH32V003A4M6</t>
@@ -552,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -703,16 +670,16 @@
         <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -720,102 +687,38 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
         <v>22</v>
       </c>
     </row>
